--- a/assets/data/excel/language.xlsx
+++ b/assets/data/excel/language.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,41 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -67,28 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,861 +413,4511 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>zh_cn</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>en_us</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>键名</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>中文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>game_title</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>霓虹深渊</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Neon Abyss</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>start_game</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>开始游戏</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Start Game</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>settings</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>设置</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>achievements</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>成就</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Achievements</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>酒馆</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Tavern</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>队伍</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>dungeon</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>禁区</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Dungeon</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>shop</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>confirm</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>确认</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>取消</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>coin</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>赛博币</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cyber Coin</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>菌丝</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mycelium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>层</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>生命</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>atk</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>暴击</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Crit</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>dodge</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>闪避</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Dodge</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>胜利</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Victory</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>defeat</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Defeat</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>explore</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>探索</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>recruit</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>招募</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Recruit</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>remove</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>移除</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>equipped</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>已装备</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Equipped</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>unequipped</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>未装备</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Unequipped</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>team_empty</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>队伍中没有成员</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Team is empty</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>team_empty_desc</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>请先招募角色并配置队伍</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Please recruit and configure team first</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>go_to_shop</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>去招募</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Go to Shop</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>team_not_full</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>队伍未配满</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Team not full</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>team_not_full_desc</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>当前队伍人数不足，是否继续进入？</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Team is not full. Continue?</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>continue</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>继续进入</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>go_to_team</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>去配置</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Go to Team</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>tavern_welcome</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>欢迎来到霓虹酒馆</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Welcome to Neon Tavern</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>bartender</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>调酒师小明</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Bartender Ming</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>ready_tip</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>准备好进入禁区了吗？</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ready to enter the dungeon?</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>enter_dungeon</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>进入禁区</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Enter Dungeon</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>tavern_hint</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>点击底部 [牢] 可快速进入禁区</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Click [Dungeon] tab to enter</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>start_explore</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>开始探索</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Start Explore</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>current_floor</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>第 {floor} 层</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Floor {floor}</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>auto_battle</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>自动战斗进行中...</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Auto battle in progress...</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>team_count</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>队伍: {count}/5 人</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Team: {count}/5</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>se_volume</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>音效音量</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>SE Volume</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>bgm_volume</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>BGM音量</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>BGM Volume</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>danger_zone</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>危险操作</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Danger Zone</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>reset_progress</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>重置进度</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Reset Progress</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>confirm_reset</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>确认重置？</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Confirm Reset?</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>reset_desc</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>所有进度将被清除\n无法恢复！</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>All progress will be lost!</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>{price} 币</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>{price} Coins</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>currency_mycelium</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>菌丝</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mycelium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>currency_mycelium_desc</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>从菌类生物身上采集的稀有资源，用于升级基地设施</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rare resource harvested from fungal creatures, used for base upgrades</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>currency_source_core</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>源核</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Source Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>currency_source_core_desc</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>蕴含原始能量的核心，用于强化装备和芯片</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Core containing primal energy, used for equipment and chip enhancement</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>currency_star_coin</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>星币</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Star Coin</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>currency_star_coin_desc</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>禁区中流通的高级货币，可在特殊商店购买稀有物品</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Premium currency in the dungeon, used in special shops for rare items</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>currency_cyber_coin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>菌丝</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mycelium</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>currency_cyber_coin_desc</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>基础交易货币，通过探索和战斗获得</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Basic trading currency, earned through exploration and combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>element_water</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>element_water_desc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>流动之力，克制火焰，被风克制</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Power of flow, strong against Fire, weak to Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>element_fire</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>element_fire_desc</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>燃烧之力，克制风，被水克制</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Power of combustion, strong against Wind, weak to Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>element_wind</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>风</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>element_wind_desc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>疾风之力，克制暗，被火克制</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Power of swiftness, strong against Dark, weak to Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>element_dark</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>暗</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>element_dark_desc</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>暗影之力，与光互克</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Power of shadow, mutual counter with Light</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>element_light</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>element_light_desc</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>圣光之力，与暗互克</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Power of radiance, mutual counter with Dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>element_advantage</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>克制</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>element_disadvantage</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>被克制</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Disadvantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>element_neutral</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>无克制</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>element_bonus_damage</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>克制伤害+{percent}%</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Advantage Damage +{percent}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>element_resist_damage</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>被克制伤害-{percent}%</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Disadvantage Damage -{percent}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>race_plant</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>植物系</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>race_plant_desc</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>与自然共生的生命体，擅长治愈和持续作战</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Nature-bound lifeforms, excel in healing and sustained combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>race_animal</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>动物系</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Animal</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>race_animal_desc</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>原始野性的化身，拥有出色的物理战斗能力</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Incarnation of primal wildness, outstanding physical combat ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>race_mech</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>机械系</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>race_mech_desc</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>高度发达的科技产物，攻防均衡且可升级</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Advanced technological creations, balanced offense and defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>race_energy</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>能量系</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>race_energy_desc</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>纯粹的能量生命体，掌控强大的元素之力</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Pure energy lifeforms, wielding powerful elemental forces</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>race_hybrid</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>混合系</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>race_hybrid_desc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>多系融合的变异体，拥有不稳定的强大力量</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Multi-line fused mutants with unstable but powerful abilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>subrace_fungus</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>菌类</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fungus</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>subrace_flower</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>花类</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Flower</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>subrace_vine</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>藤蔓</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Vine</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>subrace_tree</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>树木</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>subrace_cactus</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>仙人掌</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cactus</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>subrace_seaweed</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>水草</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>subrace_feline</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>猫科</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Feline</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>subrace_canine</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>犬科</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Canine</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>subrace_avian</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>鸟类</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Avian</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>subrace_aquatic</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Aquatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>subrace_reptile</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>爬行</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Reptile</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>subrace_insect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>昆虫</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Insect</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>subrace_warchariot</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>战车</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>War Chariot</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>subrace_drone</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>无人机</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Drone</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>subrace_medical_mech</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>医疗机械</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Medical Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>subrace_industrial</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>工业</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>subrace_military</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>军用</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Military</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>subrace_civilian</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>民用</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Civilian</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>subrace_fire_elem</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>火焰</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Fire Elemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>subrace_ice_elem</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ice Elemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>subrace_thunder_elem</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>雷电</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Thunder Elemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>subrace_light_elem</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>光能</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Light Elemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>subrace_dark_elem</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>暗能</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dark Elemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>subrace_radiation</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>辐射</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Radiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>subrace_bio_mech</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>动植混合</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bio-Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>subrace_mech_plant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>机植混合</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mech-Plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>subrace_mech_animal</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>机动混合</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mech-Animal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>subrace_energy_mix</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>能量混合</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Energy Mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>subrace_triple_mix</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>三系混合</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Triple Mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>subrace_chaos</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>混沌</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>chip_system</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>强化芯片</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Enhancement Chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>chip_quality_N</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>chip_quality_R</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>chip_quality_SR</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Super Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>chip_quality_SSR</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Super Super Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>chip_quality_UR</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>chip_quality_LE</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>神话</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>chip_equip</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>装备芯片</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Equip Chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>chip_unequip</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>卸下芯片</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Unequip Chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>chip_synthesize</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>芯片合成</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Chip Synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chip_enhance</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>芯片强化</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Chip Enhance</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>chip_enhance_success</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>强化成功！</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Enhancement Success!</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>chip_enhance_fail</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>强化失败</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Enhancement Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>chip_slot_empty</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>芯片槽位空</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chip Slot Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>chip_skill</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>芯片技能</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Chip Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>chip_target_profession</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>适用职业</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Target Profession</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>chip_target_element</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>适用元素</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Target Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chip_target_race</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>适用种族</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Target Race</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>chip_all</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>minion_system</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>随从卡</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Minion Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>minion_summon</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>召唤随从</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Summon Minion</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>minion_dismiss</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>解散随从</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dismiss Minion</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>minion_rarity_common</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>minion_rarity_rare</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>minion_rarity_epic</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>minion_rarity_legendary</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>minion_active_skill</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>主动技能</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Active Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>minion_passive_skill</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>被动技能</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Passive Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>minion_level</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>随从等级</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Minion Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>minion_exp</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>随从经验</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Minion EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>minion_evolve</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>随从进化</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Minion Evolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>status_burn</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>灼烧</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>status_burn_desc</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>每回合受到攻击力{percent}%的火焰伤害</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Takes {percent}% ATK as fire damage per turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>status_freeze</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>冻结</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>status_freeze_desc</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>无法行动，持续{turns}回合</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Unable to act for {turns} turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>status_poison</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>status_poison_desc</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>每回合受到固定毒素伤害</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Takes fixed poison damage per turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>status_bleed</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>流血</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>status_bleed_desc</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>每回合受到攻击力{percent}%的物理伤害</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Takes {percent}% ATK as physical damage per turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>status_stun</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>眩晕</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>status_stun_desc</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>无法行动1回合</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Unable to act for 1 turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>status_shield</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>status_shield_desc</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>吸收{amount}点伤害</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Absorbs {amount} damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>status_atk_up</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>攻击提升</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ATK Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>status_atk_down</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>攻击降低</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ATK Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>status_def_up</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>防御提升</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DEF Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>status_def_down</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>防御降低</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DEF Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>status_speed_up</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>速度提升</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SPD Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>status_speed_down</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>速度降低</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SPD Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>status_crit_up</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>暴击率提升</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CRIT Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>status_dodge_up</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>闪避率提升</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Dodge Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>status_damage_reduction</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>减伤</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Damage Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>status_death_mark</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>死亡标记</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Death Mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>status_death_mark_desc</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>{turns}回合后受到巨额真实伤害</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Takes massive true damage after {turns} turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>skill_type_damage</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>skill_type_heal</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>skill_type_buff</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>增益</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>skill_type_debuff</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>skill_type_summon</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>skill_type_aoe</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>群体</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>skill_type_single</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>skill_type_passive</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>被动</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>skill_cooldown</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>冷却: {turns}回合</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Cooldown: {turns} turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>skill_no_cooldown</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>无冷却</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>No Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>skill_mp_cost</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>消耗: {cost}能量</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Cost: {cost} Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>base_system</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>基地</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>base_upgrade</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>升级</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>base_max_level</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>已达最高等级</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Max Level Reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>base_upgrade_cost</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>升级费用: {cost}</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Upgrade Cost: {cost}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>base_facility_workbench</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>工作台</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Workbench</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>base_facility_chargers</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>充电桩</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Chargers</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>base_facility_hacker_terminal</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>黑客终端</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hacker Terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>base_facility_lab</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Research Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>base_facility_garden</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>生态园</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Eco Garden</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>base_facility_armory</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>军械库</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>base_facility_energy_well</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>能量井</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Energy Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>base_facility_training</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>训练场</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Training Ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>base_facility_medbay</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>医疗舱</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Medical Bay</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>base_facility_storage</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>energy_vitality_soda</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>活力苏打</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Vitality Soda</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>energy_vitality_soda_desc</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>恢复队伍全体10%最大生命值，提升探索效率</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Restores 10% max HP for entire team, boosts exploration efficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>energy_precision_fuel</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>精准燃料</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Precision Fuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>energy_precision_fuel_desc</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>提升队伍暴击率15%，持续本次探索</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Boosts team crit rate by 15% for current exploration</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>energy_battle_stimulant</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>战意激化剂</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Battle Stimulant</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>energy_battle_stimulant_desc</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>提升队伍攻击力20%，持续本次探索</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Boosts team ATK by 20% for current exploration</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>energy_guardian_elixir</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>守护合剂</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Guardian Elixir</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>energy_guardian_elixir_desc</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>提升队伍减伤率15%，持续本次探索</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Boosts team damage reduction by 15% for current exploration</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>energy_primal_essence</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>源初精华</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Primal Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>energy_primal_essence_desc</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>提升队伍全属性10%，持续本次探索</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Boosts all team stats by 10% for current exploration</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>energy_forbidden_potion</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>禁忌药剂</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Forbidden Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>energy_forbidden_potion_desc</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>大幅提升攻击力35%但降低防御10%，高风险高回报</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Greatly boosts ATK by 35% but reduces DEF by 10%, high risk high reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>reputation_system</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>声望</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Reputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>reputation_level</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>声望等级</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Reputation Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>reputation_points</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>声望点数</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Reputation Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>reputation_unlock</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>声望解锁</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Reputation Unlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>reputation_reward</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>声望奖励</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Reputation Reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>reputation_next</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>下一级: {name}（需要{points}点）</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Next: {name} ({points} points required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>equip_weapon</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>equip_armor</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>护甲</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>equip_accessory</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>饰品</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>equip_quality_common</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>equip_quality_rare</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>equip_quality_epic</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>equip_quality_legendary</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>equip_enhance</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Enhance</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>equip_set_bonus</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>套装效果</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Set Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>equip_set_active</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>套装已激活</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Set Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>boss_warning</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Boss警告</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Boss Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>boss_appear</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Boss出现！</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Boss Appears!</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>boss_phase_2</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Boss进入第二阶段！</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Boss enters Phase 2!</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>boss_defeated</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Boss已被击败！</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Boss Defeated!</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>boss_reward</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Boss掉落奖励</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Boss Drop Rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>quest_daily</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>每日任务</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Daily Quest</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>quest_weekly</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>每周任务</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Weekly Quest</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>quest_reward_claimed</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>奖励已领取</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Reward Claimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>quest_progress</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>进度: {current}/{target}</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Progress: {current}/{target}</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>quest_completed</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>quest_in_progress</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>loading</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>加载中...</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Loading...</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>error_network</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>网络错误</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Network Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>error_data</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>数据异常</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Data Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>返回</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>确定</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>开启</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>最大</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>最小</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>未解锁</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>已解锁</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>新</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>热门</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>限时</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>付费</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>daily_reset</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>每日重置</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Daily Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>weekly_reset</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>每周重置</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Weekly Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>countdown</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>剩余时间: {time}</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Time Remaining: {time}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>not_enough</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>数量不足</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Not Enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>已满</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>receive_reward</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>领取奖励</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Claim Reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>详情</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>筛选</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>sort</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>source_core</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>源核</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Source Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>star_coin</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>星币</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Star Coin</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>mycelium</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>菌丝</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Mycelium</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/language.xlsx
+++ b/assets/data/excel/language.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C265"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>霓虹深渊</t>
+          <t>废土元年</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neon Abyss</t>
+          <t>Wasteland Year One</t>
         </is>
       </c>
     </row>
@@ -538,4386 +538,5933 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tavern</t>
+          <t>sanctuary</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>酒馆</t>
+          <t>庇护所</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tavern</t>
+          <t>Sanctuary</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>admin_ada</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>队伍</t>
+          <t>管理员·艾达</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Admin Ada</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>禁区</t>
+          <t>队伍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dungeon</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>shop</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>商店</t>
+          <t>禁区</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Dungeon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>shop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>商店</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Shop</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coin</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菌丝</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mycelium</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>back</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>返回</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>close</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>生命</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>atk</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>确定</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>def</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>no</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dodge</t>
+          <t>on</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t>开启</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>On</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>off</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>胜利</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>defeat</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>最大</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Defeat</t>
+          <t>Max</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>min</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>探索</t>
+          <t>最小</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Min</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>recruit</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>招募</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Recruit</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>移除</t>
+          <t>已解锁</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Unlocked</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>equipped</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>已装备</t>
+          <t>新</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Equipped</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>unequipped</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>未装备</t>
+          <t>热门</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unequipped</t>
+          <t>Hot</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>team_empty</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>队伍中没有成员</t>
+          <t>限时</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Team is empty</t>
+          <t>Limited</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>team_empty_desc</t>
+          <t>free</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>请先招募角色并配置队伍</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Please recruit and configure team first</t>
+          <t>Free</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>go_to_shop</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>去招募</t>
+          <t>付费</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Go to Shop</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_not_full</t>
+          <t>daily_reset</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>队伍未配满</t>
+          <t>每日重置</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Team not full</t>
+          <t>Daily Reset</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_not_full_desc</t>
+          <t>weekly_reset</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>当前队伍人数不足，是否继续进入？</t>
+          <t>每周重置</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Team is not full. Continue?</t>
+          <t>Weekly Reset</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>countdown</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>继续进入</t>
+          <t>剩余时间: {time}</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Time Remaining: {time}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>go_to_team</t>
+          <t>not_enough</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>去配置</t>
+          <t>数量不足</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Go to Team</t>
+          <t>Not Enough</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tavern_welcome</t>
+          <t>full</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>欢迎来到霓虹酒馆</t>
+          <t>已满</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Welcome to Neon Tavern</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bartender</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>调酒师小明</t>
+          <t>空</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bartender Ming</t>
+          <t>Empty</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ready_tip</t>
+          <t>receive_reward</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>准备好进入禁区了吗？</t>
+          <t>领取奖励</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ready to enter the dungeon?</t>
+          <t>Claim Reward</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>enter_dungeon</t>
+          <t>detail</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>进入禁区</t>
+          <t>详情</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enter Dungeon</t>
+          <t>Details</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tavern_hint</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>点击底部 [牢] 可快速进入禁区</t>
+          <t>筛选</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Click [Dungeon] tab to enter</t>
+          <t>Filter</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>start_explore</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>开始探索</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Start Explore</t>
+          <t>Sort</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>current_floor</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>第 {floor} 层</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Floor {floor}</t>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>auto_battle</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>自动战斗进行中...</t>
+          <t>推荐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auto battle in progress...</t>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>team_count</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>队伍: {count}/5 人</t>
+          <t>加载中...</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Team: {count}/5</t>
+          <t>Loading...</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>se_volume</t>
+          <t>error_network</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>网络错误</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SE Volume</t>
+          <t>Network Error</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bgm_volume</t>
+          <t>error_data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BGM音量</t>
+          <t>数据异常</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BGM Volume</t>
+          <t>Data Error</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>danger_zone</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>危险操作</t>
+          <t>继续进入</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Danger Zone</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>reset_progress</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>重置进度</t>
+          <t>{price} 菌丝</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reset Progress</t>
+          <t>{price} Mycelium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>confirm_reset</t>
+          <t>currency_mycelium</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>确认重置？</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Confirm Reset?</t>
+          <t>Mycelium</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reset_desc</t>
+          <t>currency_mycelium_desc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>所有进度将被清除\n无法恢复！</t>
+          <t>从菌类生物身上采集的稀有资源，用于升级基地设施</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>All progress will be lost!</t>
+          <t>Rare resource harvested from fungal creatures, used for base upgrades</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>currency_source_core</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{price} 币</t>
+          <t>源核</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{price} Coins</t>
+          <t>Source Core</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>currency_mycelium</t>
+          <t>currency_source_core_desc</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>菌丝</t>
+          <t>蕴含原始能量的核心，用于强化装备和芯片</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mycelium</t>
+          <t>Core containing primal energy, used for equipment and chip enhancement</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>currency_mycelium_desc</t>
+          <t>currency_star_coin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>从菌类生物身上采集的稀有资源，用于升级基地设施</t>
+          <t>星币</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rare resource harvested from fungal creatures, used for base upgrades</t>
+          <t>Star Coin</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>currency_source_core</t>
+          <t>currency_star_coin_desc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>源核</t>
+          <t>禁区中流通的高级货币，可在特殊商店购买稀有物品</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Source Core</t>
+          <t>Premium currency in the dungeon, used in special shops for rare items</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>currency_source_core_desc</t>
+          <t>coin</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>蕴含原始能量的核心，用于强化装备和芯片</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Core containing primal energy, used for equipment and chip enhancement</t>
+          <t>Mycelium</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>currency_star_coin</t>
+          <t>mycelium</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>星币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Star Coin</t>
+          <t>Mycelium</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>currency_star_coin_desc</t>
+          <t>source_core</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>禁区中流通的高级货币，可在特殊商店购买稀有物品</t>
+          <t>源核</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Premium currency in the dungeon, used in special shops for rare items</t>
+          <t>Source Core</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>currency_cyber_coin</t>
+          <t>star_coin</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>菌丝</t>
+          <t>星币</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mycelium</t>
+          <t>Star Coin</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>currency_cyber_coin_desc</t>
+          <t>fusion_maiden</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>基础交易货币，通过探索和战斗获得</t>
+          <t>融合姬</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Basic trading currency, earned through exploration and combat</t>
+          <t>Fusion Maiden</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>element_water</t>
+          <t>fusion_maiden_desc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>通过生物融合技术诞生的战斗单位</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Combat units born through bio-fusion technology</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>element_water_desc</t>
+          <t>recruit</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>流动之力，克制火焰，被风克制</t>
+          <t>招募</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Power of flow, strong against Fire, weak to Wind</t>
+          <t>Recruit</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>element_fire</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>移除</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Remove</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>element_fire_desc</t>
+          <t>team_empty</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>燃烧之力，克制风，被水克制</t>
+          <t>队伍中没有成员</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Power of combustion, strong against Wind, weak to Water</t>
+          <t>Team is empty</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>element_wind</t>
+          <t>team_empty_desc</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>风</t>
+          <t>请先招募融合姬并配置队伍</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Please recruit Fusion Maidens and configure team first</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>element_wind_desc</t>
+          <t>go_to_shop</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>疾风之力，克制暗，被火克制</t>
+          <t>去招募</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Power of swiftness, strong against Dark, weak to Fire</t>
+          <t>Go to Shop</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>element_dark</t>
+          <t>team_not_full</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>暗</t>
+          <t>队伍未配满</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Team not full</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>element_dark_desc</t>
+          <t>team_not_full_desc</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>暗影之力，与光互克</t>
+          <t>当前队伍人数不足，是否继续进入？</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Power of shadow, mutual counter with Light</t>
+          <t>Team is not full. Continue?</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>element_light</t>
+          <t>go_to_team</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>去配置</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Go to Team</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>element_light_desc</t>
+          <t>team_count</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>圣光之力，与暗互克</t>
+          <t>队伍: {count}/4 人</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Power of radiance, mutual counter with Dark</t>
+          <t>Team: {count}/4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>element_advantage</t>
+          <t>lost_one</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>克制</t>
+          <t>失心者</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Advantage</t>
+          <t>Lost One</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>element_disadvantage</t>
+          <t>lost_one_desc</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>被克制</t>
+          <t>因辐射和变异而失去理智的生物</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Disadvantage</t>
+          <t>Creatures driven mad by radiation and mutation</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>element_neutral</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>无克制</t>
+          <t>敌人</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Enemy</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>element_bonus_damage</t>
+          <t>elite_enemy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>克制伤害+{percent}%</t>
+          <t>精英敌人</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Advantage Damage +{percent}%</t>
+          <t>Elite Enemy</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>element_resist_damage</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>被克制伤害-{percent}%</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Disadvantage Damage -{percent}%</t>
+          <t>Boss</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>race_plant</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>植物系</t>
+          <t>层</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>Floor</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>race_plant_desc</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>与自然共生的生命体，擅长治愈和持续作战</t>
+          <t>生命</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nature-bound lifeforms, excel in healing and sustained combat</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>race_animal</t>
+          <t>atk</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>动物系</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>ATK</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>race_animal_desc</t>
+          <t>def</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>原始野性的化身，拥有出色的物理战斗能力</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Incarnation of primal wildness, outstanding physical combat ability</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>race_mech</t>
+          <t>crit</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>机械系</t>
+          <t>暴击</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mech</t>
+          <t>Crit</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>race_mech_desc</t>
+          <t>dodge</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>高度发达的科技产物，攻防均衡且可升级</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Advanced technological creations, balanced offense and defense</t>
+          <t>Dodge</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>race_energy</t>
+          <t>win</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>能量系</t>
+          <t>胜利</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Victory</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>race_energy_desc</t>
+          <t>defeat</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>纯粹的能量生命体，掌控强大的元素之力</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pure energy lifeforms, wielding powerful elemental forces</t>
+          <t>Defeat</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>race_hybrid</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>混合系</t>
+          <t>探索</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Explore</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>race_hybrid_desc</t>
+          <t>equipped</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>多系融合的变异体，拥有不稳定的强大力量</t>
+          <t>已装备</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Multi-line fused mutants with unstable but powerful abilities</t>
+          <t>Equipped</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>subrace_fungus</t>
+          <t>unequipped</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>菌类</t>
+          <t>未装备</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fungus</t>
+          <t>Unequipped</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>subrace_flower</t>
+          <t>sanctuary_welcome</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>花类</t>
+          <t>欢迎来到庇护所</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Flower</t>
+          <t>Welcome to Sanctuary</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>subrace_vine</t>
+          <t>admin_hint</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>藤蔓</t>
+          <t>管理员·艾达为你提供指引</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vine</t>
+          <t>Admin Ada will guide you</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>subrace_tree</t>
+          <t>ready_tip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>树木</t>
+          <t>准备好进入禁区了吗？</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Ready to enter the dungeon?</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>subrace_cactus</t>
+          <t>enter_dungeon</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>仙人掌</t>
+          <t>进入禁区</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Enter Dungeon</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>subrace_seaweed</t>
+          <t>sanctuary_hint</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>水草</t>
+          <t>点击底部 [禁区] 可快速进入</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>Click [Dungeon] tab to enter</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>subrace_feline</t>
+          <t>start_explore</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>猫科</t>
+          <t>开始探索</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Feline</t>
+          <t>Start Explore</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>subrace_canine</t>
+          <t>current_floor</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>犬科</t>
+          <t>第 {floor} 层</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Canine</t>
+          <t>Floor {floor}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>subrace_avian</t>
+          <t>auto_battle</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>鸟类</t>
+          <t>自动战斗进行中...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avian</t>
+          <t>Auto battle in progress...</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>subrace_aquatic</t>
+          <t>se_volume</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>鱼类</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Aquatic</t>
+          <t>SE Volume</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>subrace_reptile</t>
+          <t>bgm_volume</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>爬行</t>
+          <t>BGM音量</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>BGM Volume</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>subrace_insect</t>
+          <t>danger_zone</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>昆虫</t>
+          <t>危险操作</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Danger Zone</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>subrace_warchariot</t>
+          <t>reset_progress</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>重置进度</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>War Chariot</t>
+          <t>Reset Progress</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>subrace_drone</t>
+          <t>confirm_reset</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>无人机</t>
+          <t>确认重置？</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Drone</t>
+          <t>Confirm Reset?</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>subrace_medical_mech</t>
+          <t>reset_desc</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>医疗机械</t>
+          <t>所有进度将被清除\n无法恢复！</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Medical Mech</t>
+          <t>All progress will be lost!</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>subrace_industrial</t>
+          <t>base_system</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>基地</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Base</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>subrace_military</t>
+          <t>base_upgrade</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>军用</t>
+          <t>升级</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Military</t>
+          <t>Upgrade</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>subrace_civilian</t>
+          <t>base_max_level</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>民用</t>
+          <t>已达最高等级</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Civilian</t>
+          <t>Max Level Reached</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>subrace_fire_elem</t>
+          <t>base_upgrade_cost</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>火焰</t>
+          <t>升级费用: {cost}</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fire Elemental</t>
+          <t>Upgrade Cost: {cost}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>subrace_ice_elem</t>
+          <t>base_facility_fusion_pod</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>融合舱</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ice Elemental</t>
+          <t>Fusion Pod</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>subrace_thunder_elem</t>
+          <t>base_facility_dorms</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>雷电</t>
+          <t>休眠舱</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thunder Elemental</t>
+          <t>Dorms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>subrace_light_elem</t>
+          <t>base_facility_synthesizer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>光能</t>
+          <t>合成台</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Light Elemental</t>
+          <t>Synthesizer</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>subrace_dark_elem</t>
+          <t>base_facility_training</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>暗能</t>
+          <t>训练场</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dark Elemental</t>
+          <t>Training Ground</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>subrace_radiation</t>
+          <t>base_facility_hacker</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>辐射</t>
+          <t>黑客终端</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Radiation</t>
+          <t>Hacker Terminal</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>subrace_bio_mech</t>
+          <t>base_facility_storage</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>动植混合</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bio-Mech</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>subrace_mech_plant</t>
+          <t>element_water</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>机植混合</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mech-Plant</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>subrace_mech_animal</t>
+          <t>element_water_desc</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>机动混合</t>
+          <t>流动之力，克制火焰，被风克制</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mech-Animal</t>
+          <t>Power of flow, strong against Fire, weak to Wind</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>subrace_energy_mix</t>
+          <t>element_fire</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>能量混合</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Energy Mix</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>subrace_triple_mix</t>
+          <t>element_fire_desc</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>三系混合</t>
+          <t>燃烧之力，克制风，被水克制</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Triple Mix</t>
+          <t>Power of combustion, strong against Wind, weak to Water</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>subrace_chaos</t>
+          <t>element_wind</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>混沌</t>
+          <t>风</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chaos</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chip_system</t>
+          <t>element_wind_desc</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>强化芯片</t>
+          <t>疾风之力，克制暗，被火克制</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Enhancement Chip</t>
+          <t>Power of swiftness, strong against Dark, weak to Fire</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chip_quality_N</t>
+          <t>element_dark</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>暗</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>chip_quality_R</t>
+          <t>element_dark_desc</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>暗影之力，与光互克</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Power of shadow, mutual counter with Light</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>chip_quality_SR</t>
+          <t>element_light</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>光</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Super Rare</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>chip_quality_SSR</t>
+          <t>element_light_desc</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>传说</t>
+          <t>净化之光，与暗互克</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Super Super Rare</t>
+          <t>Power of radiance, mutual counter with Dark</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chip_quality_UR</t>
+          <t>element_advantage</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>克制</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Advantage</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chip_quality_LE</t>
+          <t>element_disadvantage</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>神话</t>
+          <t>被克制</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Disadvantage</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chip_equip</t>
+          <t>element_neutral</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>装备芯片</t>
+          <t>无克制</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Equip Chip</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>chip_unequip</t>
+          <t>element_bonus_damage</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>卸下芯片</t>
+          <t>克制伤害+{percent}%</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Unequip Chip</t>
+          <t>Advantage Damage +{percent}%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chip_synthesize</t>
+          <t>element_resist_damage</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>芯片合成</t>
+          <t>被克制伤害-{percent}%</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chip Synthesis</t>
+          <t>Disadvantage Damage -{percent}%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>chip_enhance</t>
+          <t>race_plant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>芯片强化</t>
+          <t>植物系</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chip Enhance</t>
+          <t>Plant</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chip_enhance_success</t>
+          <t>race_plant_desc</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>强化成功！</t>
+          <t>与自然共生的生命体，擅长治愈和持续作战</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Enhancement Success!</t>
+          <t>Nature-bound lifeforms, excel in healing and sustained combat</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>chip_enhance_fail</t>
+          <t>race_animal</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>强化失败</t>
+          <t>动物系</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Enhancement Failed</t>
+          <t>Animal</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>chip_slot_empty</t>
+          <t>race_animal_desc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>芯片槽位空</t>
+          <t>原始野性的化身，拥有出色的物理战斗能力</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chip Slot Empty</t>
+          <t>Incarnation of primal wildness, outstanding physical combat ability</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>chip_skill</t>
+          <t>race_mech</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>芯片技能</t>
+          <t>机械系</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chip Skill</t>
+          <t>Mech</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chip_target_profession</t>
+          <t>race_mech_desc</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>适用职业</t>
+          <t>高度发达的科技产物，攻防均衡且可升级</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Target Profession</t>
+          <t>Advanced technological creations, balanced offense and defense</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>chip_target_element</t>
+          <t>race_energy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>适用元素</t>
+          <t>能量系</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Target Element</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chip_target_race</t>
+          <t>race_energy_desc</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>适用种族</t>
+          <t>纯粹的能量生命体，掌控强大的元素之力</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Target Race</t>
+          <t>Pure energy lifeforms, wielding powerful elemental forces</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chip_all</t>
+          <t>race_hybrid</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>混合系</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>minion_system</t>
+          <t>race_hybrid_desc</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>随从卡</t>
+          <t>多系融合的变异体，拥有不稳定的强大力量</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minion Card</t>
+          <t>Multi-line fused mutants with unstable but powerful abilities</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>minion_summon</t>
+          <t>subrace_fungus</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>召唤随从</t>
+          <t>菌类</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Summon Minion</t>
+          <t>Fungus</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>minion_dismiss</t>
+          <t>subrace_flower</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>解散随从</t>
+          <t>花类</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dismiss Minion</t>
+          <t>Flower</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>minion_rarity_common</t>
+          <t>subrace_vine</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>藤蔓</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Vine</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>minion_rarity_rare</t>
+          <t>subrace_tree</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>树木</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tree</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>minion_rarity_epic</t>
+          <t>subrace_cactus</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>仙人掌</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Cactus</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>minion_rarity_legendary</t>
+          <t>subrace_seaweed</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>传说</t>
+          <t>水草</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Seaweed</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>minion_active_skill</t>
+          <t>subrace_feline</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>主动技能</t>
+          <t>猫科</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Active Skill</t>
+          <t>Feline</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>minion_passive_skill</t>
+          <t>subrace_canine</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>被动技能</t>
+          <t>犬科</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Passive Skill</t>
+          <t>Canine</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>minion_level</t>
+          <t>subrace_avian</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>随从等级</t>
+          <t>鸟类</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Minion Level</t>
+          <t>Avian</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>minion_exp</t>
+          <t>subrace_aquatic</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>随从经验</t>
+          <t>鱼类</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Minion EXP</t>
+          <t>Aquatic</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>minion_evolve</t>
+          <t>subrace_reptile</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>随从进化</t>
+          <t>爬行</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Minion Evolve</t>
+          <t>Reptile</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>status_burn</t>
+          <t>subrace_insect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>灼烧</t>
+          <t>昆虫</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Insect</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>status_burn_desc</t>
+          <t>subrace_warchariot</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>每回合受到攻击力{percent}%的火焰伤害</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Takes {percent}% ATK as fire damage per turn</t>
+          <t>War Chariot</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>status_freeze</t>
+          <t>subrace_drone</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>冻结</t>
+          <t>无人机</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Drone</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>status_freeze_desc</t>
+          <t>subrace_medical_mech</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>无法行动，持续{turns}回合</t>
+          <t>医疗机械</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Unable to act for {turns} turns</t>
+          <t>Medical Mech</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>status_poison</t>
+          <t>subrace_industrial</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>中毒</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>status_poison_desc</t>
+          <t>subrace_military</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>每回合受到固定毒素伤害</t>
+          <t>军用</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Takes fixed poison damage per turn</t>
+          <t>Military</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>status_bleed</t>
+          <t>subrace_civilian</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>流血</t>
+          <t>民用</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bleed</t>
+          <t>Civilian</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>status_bleed_desc</t>
+          <t>subrace_fire_elem</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>每回合受到攻击力{percent}%的物理伤害</t>
+          <t>火焰</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Takes {percent}% ATK as physical damage per turn</t>
+          <t>Fire Elemental</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>status_stun</t>
+          <t>subrace_ice_elem</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>寒冰</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Stun</t>
+          <t>Ice Elemental</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>status_stun_desc</t>
+          <t>subrace_thunder_elem</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>无法行动1回合</t>
+          <t>雷电</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Unable to act for 1 turn</t>
+          <t>Thunder Elemental</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>status_shield</t>
+          <t>subrace_light_elem</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>光能</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Light Elemental</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>status_shield_desc</t>
+          <t>subrace_dark_elem</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>吸收{amount}点伤害</t>
+          <t>暗能</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Absorbs {amount} damage</t>
+          <t>Dark Elemental</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>status_atk_up</t>
+          <t>subrace_radiation</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>攻击提升</t>
+          <t>辐射</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Radiation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>status_atk_down</t>
+          <t>subrace_bio_mech</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>攻击降低</t>
+          <t>动植混合</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ATK Down</t>
+          <t>Bio-Mech</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>status_def_up</t>
+          <t>subrace_mech_plant</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>防御提升</t>
+          <t>机植混合</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DEF Up</t>
+          <t>Mech-Plant</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>status_def_down</t>
+          <t>subrace_mech_animal</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>防御降低</t>
+          <t>机动混合</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DEF Down</t>
+          <t>Mech-Animal</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>status_speed_up</t>
+          <t>subrace_energy_mix</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>速度提升</t>
+          <t>能量混合</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SPD Up</t>
+          <t>Energy Mix</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>status_speed_down</t>
+          <t>subrace_triple_mix</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>速度降低</t>
+          <t>三系混合</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SPD Down</t>
+          <t>Triple Mix</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>status_crit_up</t>
+          <t>subrace_chaos</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>暴击率提升</t>
+          <t>混沌</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CRIT Up</t>
+          <t>Chaos</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>status_dodge_up</t>
+          <t>profession_tank</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>闪避率提升</t>
+          <t>坦克</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dodge Up</t>
+          <t>Tank</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>status_damage_reduction</t>
+          <t>profession_tank_desc</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>减伤</t>
+          <t>高生命高防御，负责承受伤害保护队友</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Damage Reduction</t>
+          <t>High HP and DEF, protects teammates by absorbing damage</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>status_death_mark</t>
+          <t>profession_dps</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>死亡标记</t>
+          <t>输出</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Death Mark</t>
+          <t>DPS</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>status_death_mark_desc</t>
+          <t>profession_dps_desc</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>{turns}回合后受到巨额真实伤害</t>
+          <t>高攻击高暴击，负责对敌人造成大量伤害</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Takes massive true damage after {turns} turns</t>
+          <t>High ATK and CRIT, deals massive damage to enemies</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>skill_type_damage</t>
+          <t>profession_support</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>辅助</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>skill_type_heal</t>
+          <t>profession_support_desc</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>提供治疗和增益效果，保障队伍续航</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Provides healing and buffs, ensures team sustainability</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>skill_type_buff</t>
+          <t>quality_N</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>增益</t>
+          <t>N-普通</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>N-Normal</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>skill_type_debuff</t>
+          <t>quality_R</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>减益</t>
+          <t>R-稀有</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Debuff</t>
+          <t>R-Rare</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>skill_type_summon</t>
+          <t>quality_SR</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>SR-精英</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Summon</t>
+          <t>SR-Super Rare</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>skill_type_aoe</t>
+          <t>quality_SSR</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>群体</t>
+          <t>SSR-传说</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AOE</t>
+          <t>SSR-Super Super Rare</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>skill_type_single</t>
+          <t>quality_UR</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>UR-史诗</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>UR-Ultra Rare</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>skill_type_passive</t>
+          <t>quality_LE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>LE-绝世</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>LE-Legendary Exclusive</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>skill_cooldown</t>
+          <t>chip_system</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>冷却: {turns}回合</t>
+          <t>强化芯片</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cooldown: {turns} turns</t>
+          <t>Enhancement Chip</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>skill_no_cooldown</t>
+          <t>chip_quality_N</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>无冷却</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No Cooldown</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>skill_mp_cost</t>
+          <t>chip_quality_R</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>消耗: {cost}能量</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cost: {cost} Energy</t>
+          <t>Rare</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>base_system</t>
+          <t>chip_quality_SR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>基地</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Super Rare</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>base_upgrade</t>
+          <t>chip_quality_SSR</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>升级</t>
+          <t>传说</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>Super Super Rare</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>base_max_level</t>
+          <t>chip_quality_UR</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>已达最高等级</t>
+          <t>史诗</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Max Level Reached</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>base_upgrade_cost</t>
+          <t>chip_quality_LE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>升级费用: {cost}</t>
+          <t>绝世</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Upgrade Cost: {cost}</t>
+          <t>Legendary Exclusive</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>base_facility_workbench</t>
+          <t>chip_equip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>工作台</t>
+          <t>装备芯片</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Workbench</t>
+          <t>Equip Chip</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>base_facility_chargers</t>
+          <t>chip_unequip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>充电桩</t>
+          <t>卸下芯片</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chargers</t>
+          <t>Unequip Chip</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>base_facility_hacker_terminal</t>
+          <t>chip_synthesize</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>黑客终端</t>
+          <t>芯片合成</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hacker Terminal</t>
+          <t>Chip Synthesis</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>base_facility_lab</t>
+          <t>chip_enhance</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>芯片强化</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Research Lab</t>
+          <t>Chip Enhance</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>base_facility_garden</t>
+          <t>chip_enhance_success</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>生态园</t>
+          <t>强化成功！</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Eco Garden</t>
+          <t>Enhancement Success!</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>base_facility_armory</t>
+          <t>chip_enhance_fail</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>军械库</t>
+          <t>强化失败</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Armory</t>
+          <t>Enhancement Failed</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>base_facility_energy_well</t>
+          <t>chip_slot_empty</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>能量井</t>
+          <t>芯片槽位空</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Energy Well</t>
+          <t>Chip Slot Empty</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>base_facility_training</t>
+          <t>chip_skill</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>训练场</t>
+          <t>芯片技能</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Training Ground</t>
+          <t>Chip Skill</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>base_facility_medbay</t>
+          <t>chip_target_profession</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>医疗舱</t>
+          <t>适用职业</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Medical Bay</t>
+          <t>Target Profession</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>base_facility_storage</t>
+          <t>chip_target_element</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>适用元素</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Target Element</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>energy_vitality_soda</t>
+          <t>chip_target_race</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>活力苏打</t>
+          <t>适用种族</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Vitality Soda</t>
+          <t>Target Race</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>energy_vitality_soda_desc</t>
+          <t>chip_all</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>恢复队伍全体10%最大生命值，提升探索效率</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Restores 10% max HP for entire team, boosts exploration efficiency</t>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>energy_precision_fuel</t>
+          <t>minion_system</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>精准燃料</t>
+          <t>随从卡</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Precision Fuel</t>
+          <t>Minion Card</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>energy_precision_fuel_desc</t>
+          <t>minion_summon</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>提升队伍暴击率15%，持续本次探索</t>
+          <t>召唤随从</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boosts team crit rate by 15% for current exploration</t>
+          <t>Summon Minion</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>energy_battle_stimulant</t>
+          <t>minion_dismiss</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>战意激化剂</t>
+          <t>解散随从</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Battle Stimulant</t>
+          <t>Dismiss Minion</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>energy_battle_stimulant_desc</t>
+          <t>minion_rarity_common</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>提升队伍攻击力20%，持续本次探索</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Boosts team ATK by 20% for current exploration</t>
+          <t>Common</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>energy_guardian_elixir</t>
+          <t>minion_rarity_rare</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>守护合剂</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Guardian Elixir</t>
+          <t>Rare</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>energy_guardian_elixir_desc</t>
+          <t>minion_rarity_epic</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>提升队伍减伤率15%，持续本次探索</t>
+          <t>史诗</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Boosts team damage reduction by 15% for current exploration</t>
+          <t>Epic</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>energy_primal_essence</t>
+          <t>minion_rarity_legendary</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>源初精华</t>
+          <t>传说</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Primal Essence</t>
+          <t>Legendary</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>energy_primal_essence_desc</t>
+          <t>minion_active_skill</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>提升队伍全属性10%，持续本次探索</t>
+          <t>主动技能</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Boosts all team stats by 10% for current exploration</t>
+          <t>Active Skill</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>energy_forbidden_potion</t>
+          <t>minion_passive_skill</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>禁忌药剂</t>
+          <t>被动技能</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Forbidden Potion</t>
+          <t>Passive Skill</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>energy_forbidden_potion_desc</t>
+          <t>minion_level</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>大幅提升攻击力35%但降低防御10%，高风险高回报</t>
+          <t>随从等级</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Greatly boosts ATK by 35% but reduces DEF by 10%, high risk high reward</t>
+          <t>Minion Level</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>reputation_system</t>
+          <t>minion_exp</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>随从经验</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Minion EXP</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>reputation_level</t>
+          <t>minion_evolve</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>声望等级</t>
+          <t>随从进化</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Reputation Level</t>
+          <t>Minion Evolve</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>reputation_points</t>
+          <t>status_burn</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>声望点数</t>
+          <t>灼烧</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Reputation Points</t>
+          <t>Burn</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>reputation_unlock</t>
+          <t>status_burn_desc</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>声望解锁</t>
+          <t>每回合受到攻击力{percent}%的火焰伤害</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Reputation Unlock</t>
+          <t>Takes {percent}% ATK as fire damage per turn</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>reputation_reward</t>
+          <t>status_freeze</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>声望奖励</t>
+          <t>冻结</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Reputation Reward</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>reputation_next</t>
+          <t>status_freeze_desc</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>下一级: {name}（需要{points}点）</t>
+          <t>无法行动，持续{turns}回合</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Next: {name} ({points} points required)</t>
+          <t>Unable to act for {turns} turns</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>equip_weapon</t>
+          <t>status_poison</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>武器</t>
+          <t>中毒</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Poison</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>equip_armor</t>
+          <t>status_poison_desc</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>护甲</t>
+          <t>每回合受到固定毒素伤害</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Takes fixed poison damage per turn</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>equip_accessory</t>
+          <t>status_bleed</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>饰品</t>
+          <t>流血</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Bleed</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>equip_quality_common</t>
+          <t>status_bleed_desc</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>每回合受到攻击力{percent}%的物理伤害</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Takes {percent}% ATK as physical damage per turn</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>equip_quality_rare</t>
+          <t>status_stun</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Stun</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>equip_quality_epic</t>
+          <t>status_stun_desc</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>无法行动1回合</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Unable to act for 1 turn</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>equip_quality_legendary</t>
+          <t>status_shield</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>传说</t>
+          <t>护盾</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Shield</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>equip_enhance</t>
+          <t>status_shield_desc</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>吸收{amount}点伤害</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Absorbs {amount} damage</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>equip_set_bonus</t>
+          <t>status_atk_up</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>套装效果</t>
+          <t>攻击提升</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Set Bonus</t>
+          <t>ATK Up</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>equip_set_active</t>
+          <t>status_atk_down</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>套装已激活</t>
+          <t>攻击降低</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Set Active</t>
+          <t>ATK Down</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>boss_warning</t>
+          <t>status_def_up</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Boss警告</t>
+          <t>防御提升</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Boss Warning</t>
+          <t>DEF Up</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>boss_appear</t>
+          <t>status_def_down</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Boss出现！</t>
+          <t>防御降低</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Boss Appears!</t>
+          <t>DEF Down</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>boss_phase_2</t>
+          <t>status_speed_up</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Boss进入第二阶段！</t>
+          <t>速度提升</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Boss enters Phase 2!</t>
+          <t>SPD Up</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>boss_defeated</t>
+          <t>status_speed_down</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Boss已被击败！</t>
+          <t>速度降低</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Boss Defeated!</t>
+          <t>SPD Down</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>boss_reward</t>
+          <t>status_crit_up</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Boss掉落奖励</t>
+          <t>暴击率提升</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Boss Drop Rewards</t>
+          <t>CRIT Up</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>quest_daily</t>
+          <t>status_dodge_up</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>每日任务</t>
+          <t>闪避率提升</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Daily Quest</t>
+          <t>Dodge Up</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>quest_weekly</t>
+          <t>status_damage_reduction</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>每周任务</t>
+          <t>减伤</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Weekly Quest</t>
+          <t>Damage Reduction</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>quest_reward_claimed</t>
+          <t>status_death_mark</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>奖励已领取</t>
+          <t>死亡标记</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Reward Claimed</t>
+          <t>Death Mark</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>quest_progress</t>
+          <t>status_death_mark_desc</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>进度: {current}/{target}</t>
+          <t>{turns}回合后受到巨额真实伤害</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Progress: {current}/{target}</t>
+          <t>Takes massive true damage after {turns} turns</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>quest_completed</t>
+          <t>skill_type_damage</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Damage</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>quest_in_progress</t>
+          <t>skill_type_heal</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Heal</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>skill_type_buff</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>加载中...</t>
+          <t>增益</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Buff</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>error_network</t>
+          <t>skill_type_debuff</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>网络错误</t>
+          <t>减益</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Network Error</t>
+          <t>Debuff</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>error_data</t>
+          <t>skill_type_summon</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>数据异常</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Data Error</t>
+          <t>Summon</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>skill_type_aoe</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>返回</t>
+          <t>群体</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>AOE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>skill_type_single</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>skill_type_passive</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>确定</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Passive</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>skill_cooldown</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>冷却: {turns}回合</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cooldown: {turns} turns</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>skill_no_cooldown</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>无冷却</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No Cooldown</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>skill_mp_cost</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>开启</t>
+          <t>消耗: {cost}能量</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Cost: {cost} Energy</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>energy_vitality_soda</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>活力苏打</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Vitality Soda</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>energy_vitality_soda_desc</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>最大</t>
+          <t>恢复队伍全体10%最大生命值，提升探索效率</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Restores 10% max HP for entire team, boosts exploration efficiency</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>energy_precision_fuel</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>精准燃料</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Precision Fuel</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>energy_precision_fuel_desc</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>提升队伍暴击率15%，持续本次探索</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Boosts team crit rate by 15% for current exploration</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>unlocked</t>
+          <t>energy_battle_stimulant</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>已解锁</t>
+          <t>战意激化剂</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Unlocked</t>
+          <t>Battle Stimulant</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>energy_battle_stimulant_desc</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>新</t>
+          <t>提升队伍攻击力20%，持续本次探索</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Boosts team ATK by 20% for current exploration</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>energy_guardian_elixir</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>热门</t>
+          <t>守护合剂</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Guardian Elixir</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>energy_guardian_elixir_desc</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>限时</t>
+          <t>提升队伍减伤率15%，持续本次探索</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Boosts team damage reduction by 15% for current exploration</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>energy_primal_essence</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>源初精华</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Primal Essence</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>energy_primal_essence_desc</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>付费</t>
+          <t>提升队伍全属性10%，持续本次探索</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Boosts all team stats by 10% for current exploration</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>daily_reset</t>
+          <t>energy_forbidden_potion</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>每日重置</t>
+          <t>禁忌药剂</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Daily Reset</t>
+          <t>Forbidden Potion</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>weekly_reset</t>
+          <t>energy_forbidden_potion_desc</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>每周重置</t>
+          <t>大幅提升攻击力35%但降低防御10%，高风险高回报</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Weekly Reset</t>
+          <t>Greatly boosts ATK by 35% but reduces DEF by 10%, high risk high reward</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>countdown</t>
+          <t>reputation_system</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>剩余时间: {time}</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Time Remaining: {time}</t>
+          <t>Reputation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>not_enough</t>
+          <t>reputation_level</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>数量不足</t>
+          <t>声望等级</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Not Enough</t>
+          <t>Reputation Level</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>reputation_points</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>已满</t>
+          <t>声望点数</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Reputation Points</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>reputation_unlock</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>声望解锁</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Reputation Unlock</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>receive_reward</t>
+          <t>reputation_reward</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>领取奖励</t>
+          <t>声望奖励</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Claim Reward</t>
+          <t>Reputation Reward</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>reputation_next</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>下一级: 等级{level}（需要{points}经验）</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Next: Level {level} ({points} exp required)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>equip_weapon</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>筛选</t>
+          <t>武器</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Weapon</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>equip_armor</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>护甲</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Armor</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>equip_accessory</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>饰品</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Accessory</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>equip_quality_N</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>推荐</t>
+          <t>N-普通</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>N-Normal</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>source_core</t>
+          <t>equip_quality_R</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>源核</t>
+          <t>R-稀有</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Source Core</t>
+          <t>R-Rare</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>star_coin</t>
+          <t>equip_quality_SR</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>星币</t>
+          <t>SR-精英</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Star Coin</t>
+          <t>SR-Super Rare</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>mycelium</t>
+          <t>equip_quality_SSR</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>菌丝</t>
+          <t>SSR-传说</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Mycelium</t>
+          <t>SSR-Super Super Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>equip_quality_UR</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>UR-史诗</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>UR-Ultra Rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>equip_quality_LE</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>LE-绝世</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>LE-Legendary Exclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>equip_enhance</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Enhance</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>equip_set_bonus</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>套装效果</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Set Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>equip_set_active</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>套装已激活</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Set Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>boss_warning</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Boss警告</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Boss Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>boss_appear</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Boss出现！</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Boss Appears!</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>boss_phase_2</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Boss进入第二阶段！</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Boss enters Phase 2!</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>boss_defeated</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Boss已被击败！</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Boss Defeated!</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>boss_reward</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Boss掉落奖励</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Boss Drop Rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>quest_daily</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>每日任务</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Daily Quest</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>quest_weekly</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>每周任务</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Weekly Quest</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>quest_reward_claimed</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>奖励已领取</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Reward Claimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>quest_progress</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>进度: {current}/{target}</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Progress: {current}/{target}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>quest_completed</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>quest_in_progress</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>gacha_title</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>融合召唤</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Fusion Summon</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>gacha_single</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>单次召唤</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Summon x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>gacha_ten</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>十连召唤</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Summon x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>gacha_result</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>召唤结果</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Summon Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>gacha_pity</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>保底次数: {current}/{max}</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Pity: {current}/{max}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>gacha_new</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>gacha_duplicate</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>gacha_fragment</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>碎片</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Fragment</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>gacha_exchange</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>碎片兑换</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Fragment Exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>gacha_pool_normal</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>常驻池</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Standard Pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>gacha_pool_limited</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>限定池</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Limited Pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>gacha_pool_banner</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>UP池</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Rate-Up Pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>gacha_cost_single</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>消耗: {cost}星币</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Cost: {cost} Star Coins</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>gacha_cost_ten</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>消耗: {cost}星币</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Cost: {cost} Star Coins</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>gacha_animation_skip</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>跳过动画</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Skip Animation</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>item_title</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>背包</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>item_use</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>使用</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>item_sell</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>出售</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>item_equip</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>装备</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>item_detail</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>道具详情</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Item Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>item_quantity</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>数量: {count}</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Quantity: {count}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>item_sort_by_quality</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>按品质排序</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Sort by Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>item_sort_by_type</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>按类型排序</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Sort by Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>item_sort_by_level</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>按等级排序</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Sort by Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>item_no_item</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>背包为空</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Inventory is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>item_rad_medicine</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>抗辐射药剂</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Rad Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>item_rad_medicine_desc</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>降低辐射值，防止融合姬变异</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Reduces radiation level, prevents Fusion Maiden mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>item_antidote</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>解毒剂</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Antidote</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>item_antidote_desc</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>解除中毒状态</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Cures poison status</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>item_repair_kit</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>修复包</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Repair Kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>item_repair_kit_desc</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>修复装备耐久度</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Restores equipment durability</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>item_exp_book</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>经验芯片</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>EXP Chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>item_exp_book_desc</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>为融合姬提供经验值</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Grants EXP to Fusion Maiden</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>item_golden_key</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>黄金钥匙</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Golden Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>item_golden_key_desc</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>开启黄金宝箱</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Opens golden chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>map_sanctuary</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>庇护所外围</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Sanctuary Outskirts</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>map_mine</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>废弃矿区</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Abandoned Mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>map_aqua</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>沉没水城</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Sunken Aquapolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>map_tree</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>腐化丛林</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Corrupted Jungle</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>map_deep</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>深海遗迹</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Deep Sea Ruins</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>map_hq</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>军事要塞</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Military Fortress</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>map_spring</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>荧光温泉</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Luminous Hot Springs</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>map_arsenal</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>机械军火库</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Mech Arsenal</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>map_core</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>方舟核心</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Ark Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>map_omega</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>终焉之地</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Terminal Wasteland</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>zone_fungal_cave</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>菌丝洞穴</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Fungal Cavern</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>zone_rust_factory</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>锈蚀工厂</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Rust Factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>zone_toxic_swamp</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>剧毒沼泽</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Toxic Swamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>zone_crystal_mine</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>水晶矿洞</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Crystal Mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>zone_abandoned_lab</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>废弃实验室</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Abandoned Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>zone_radiation_desert</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>辐射荒漠</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Radiation Desert</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>zone_mutant_forest</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>变异森林</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Mutant Forest</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>zone_underground_city</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>地下城市</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Underground City</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>zone_frozen_bunker</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>冰冻地堡</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Frozen Bunker</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>zone_volcanic_rift</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>熔岩裂谷</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Volcanic Rift</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>zone_signal_tower</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>信号塔</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Signal Tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>zone_gene_vault</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>基因库</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Gene Vault</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>zone_dark_tunnel</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>暗黑隧道</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Dark Tunnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>zone_overgrown_ruins</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>蔓生废墟</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Overgrown Ruins</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>zone_storm_peak</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>风暴之巅</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Storm Peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>zone_quantum_lab</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>量子实验室</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Quantum Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>zone_bone_yard</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>白骨荒原</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Bone Yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>zone_neon_graveyard</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>霓虹墓地</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Neon Graveyard</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>zone_silent_port</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>寂静港口</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Silent Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>zone_omega_gate</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>终焉之门</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Omega Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>boss_fungal_overlord</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>菌丝领主</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Fungal Overlord</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>boss_rust_golem</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>锈蚀巨像</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Rust Golem</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>boss_toxic_queen</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>剧毒蜂后</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Toxic Queen</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>boss_crystal_titan</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>水晶泰坦</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Crystal Titan</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>boss_mutant_king</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>变异之王</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Mutant King</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>boss_cyber_dragon</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>机械龙</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Cyber Dragon</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>boss_radiation_giant</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>辐射巨人</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Radiation Giant</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>boss_quantum_wraith</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>量子幻影</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Quantum Phantom</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>boss_gene_colossus</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>基因巨兽</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Gene Colossus</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>boss_omega_sentinel</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>终焉守卫</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Omega Sentinel</t>
         </is>
       </c>
     </row>
